--- a/出張精算データ一式/20期評価者・承認者一覧_20260401.xlsx
+++ b/出張精算データ一式/20期評価者・承認者一覧_20260401.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" name="20期" sheetId="1"/>
@@ -516,7 +516,15 @@
       <name val="ＭＳ Ｐゴシック"/>
     </font>
     <font>
-      <b val="0"/>
+      <b/>
+      <i val="0"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <i val="0"/>
       <sz val="11"/>
       <color auto="1"/>
@@ -524,10 +532,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="0"/>
       <i val="0"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color auto="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <scheme val="minor"/>
     </font>
@@ -551,15 +559,7 @@
       <b/>
       <i val="0"/>
       <sz val="11"/>
-      <color auto="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <scheme val="minor"/>
     </font>
@@ -573,16 +573,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
@@ -593,7 +583,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,31 +606,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -652,13 +655,57 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -694,16 +741,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -716,32 +768,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -751,28 +777,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -788,10 +792,10 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
-      </top>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -801,31 +805,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -904,11 +888,48 @@
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -928,6 +949,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -935,9 +978,35 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -965,54 +1034,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1029,10 +1050,25 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
+      <top style="double">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -1044,49 +1080,9 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -1094,8 +1090,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -1118,119 +1118,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0">
@@ -1242,274 +1242,274 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="2"/>
-    <cellStyle name="桁区切り 2" xfId="1"/>
+    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle name="桁区切り 2" xfId="2"/>
     <cellStyle name="標準 2" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1825,7 +1825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{80A407BC-F59B-4066-9290-EE235D69C3C5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{21375689-DFEA-41B2-B22D-F631D0951DF9}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <tabColor rgb="FF00FFFF"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1854,7 +1854,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" ht="12.997499999999997" customHeight="1">
+    <row r="64" ht="12.75" customHeight="1">
       <c r="L64" s="94"/>
     </row>
   </sheetData>
@@ -3775,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A77623D8-5279-4B83-980E-18CACEE6D5C8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{73B8650D-39DD-408F-84B2-AC91D80E3ACE}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <tabColor theme="1" tint="0.05"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3804,7 +3804,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" ht="12.997499999999997" customHeight="1">
+    <row r="62" ht="12.75" customHeight="1">
       <c r="L62" s="94"/>
     </row>
   </sheetData>
@@ -5665,7 +5665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{534904BC-07DA-4C9D-9986-01D18B0566E5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{69EAB127-4911-4571-A967-0CF44DFAC010}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5696,7 +5696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="21"/>
       <c r="C4" s="6"/>
       <c r="D4" s="22"/>
@@ -5786,7 +5786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="21"/>
       <c r="C5" s="6"/>
       <c r="D5" s="22"/>
@@ -5818,7 +5818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="21"/>
       <c r="C6" s="6"/>
       <c r="D6" s="22"/>
@@ -5864,7 +5864,7 @@
       <c r="L7" s="31"/>
       <c r="M7" s="32"/>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="58" t="s">
         <v>90</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="101"/>
@@ -5930,7 +5930,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
       <c r="D10" s="55" t="s">
@@ -5964,7 +5964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="49"/>
@@ -5999,7 +5999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="49"/>
@@ -6031,7 +6031,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
       <c r="D13" s="26"/>
@@ -6063,7 +6063,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="55" t="s">
@@ -6097,7 +6097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="102"/>
       <c r="C15" s="103"/>
       <c r="D15" s="26"/>
@@ -6143,7 +6143,7 @@
       <c r="L16" s="31"/>
       <c r="M16" s="32"/>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="58" t="s">
         <v>37</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="18" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A18" s="61"/>
       <c r="B18" s="21"/>
       <c r="C18" s="6"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="N18" s="61"/>
     </row>
-    <row r="19" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="19" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A19" s="61"/>
       <c r="B19" s="21"/>
       <c r="C19" s="6"/>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="N19" s="61"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="20" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A20" s="61"/>
       <c r="B20" s="102"/>
       <c r="C20" s="104"/>
@@ -6293,7 +6293,7 @@
       <c r="L21" s="31"/>
       <c r="M21" s="32"/>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="58" t="s">
         <v>42</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="21"/>
       <c r="C23" s="6"/>
       <c r="D23" s="22"/>
@@ -6359,7 +6359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="21"/>
       <c r="C24" s="6"/>
       <c r="D24" s="22"/>
@@ -6391,7 +6391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="102"/>
       <c r="C25" s="104"/>
       <c r="D25" s="103"/>
@@ -6437,7 +6437,7 @@
       <c r="L26" s="31"/>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="105" t="s">
         <v>93</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="66"/>
       <c r="C29" s="22"/>
       <c r="D29" s="70"/>
@@ -6539,7 +6539,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="66"/>
       <c r="C30" s="22"/>
       <c r="D30" s="70"/>
@@ -6571,7 +6571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="66"/>
       <c r="C31" s="22"/>
       <c r="D31" s="70"/>
@@ -6603,7 +6603,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="66"/>
       <c r="C32" s="22"/>
       <c r="D32" s="70"/>
@@ -6635,7 +6635,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="66"/>
       <c r="C33" s="22"/>
       <c r="D33" s="70"/>
@@ -6667,7 +6667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="66"/>
       <c r="C34" s="22"/>
       <c r="D34" s="70"/>
@@ -6699,7 +6699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="66"/>
       <c r="C35" s="22"/>
       <c r="D35" s="70"/>
@@ -6731,7 +6731,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="66"/>
       <c r="C36" s="22"/>
       <c r="D36" s="75"/>
@@ -6763,7 +6763,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="66"/>
       <c r="C37" s="22"/>
       <c r="D37" s="67" t="s">
@@ -6797,7 +6797,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" ht="12.997499999999997" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="B38" s="66"/>
       <c r="C38" s="22"/>
       <c r="D38" s="49"/>
@@ -6829,7 +6829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="66"/>
       <c r="C39" s="22"/>
       <c r="D39" s="49"/>
@@ -6861,7 +6861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="66"/>
       <c r="C40" s="22"/>
       <c r="D40" s="49"/>
@@ -6893,7 +6893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="66"/>
       <c r="C41" s="22"/>
       <c r="D41" s="49"/>
@@ -7025,7 +7025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="66"/>
       <c r="C45" s="22"/>
       <c r="D45" s="70"/>
@@ -7057,7 +7057,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="66"/>
       <c r="C46" s="22"/>
       <c r="D46" s="70"/>
@@ -7089,7 +7089,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="66"/>
       <c r="C47" s="22"/>
       <c r="D47" s="70"/>
@@ -7121,7 +7121,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="66"/>
       <c r="C48" s="22"/>
       <c r="D48" s="70"/>
@@ -7153,7 +7153,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="66"/>
       <c r="C49" s="22"/>
       <c r="D49" s="70"/>
@@ -7185,7 +7185,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="66"/>
       <c r="C50" s="22"/>
       <c r="D50" s="70"/>
@@ -7217,7 +7217,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" ht="12.997499999999997" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="66"/>
       <c r="C51" s="22"/>
       <c r="D51" s="70"/>
@@ -7249,7 +7249,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="66"/>
       <c r="C52" s="22"/>
       <c r="D52" s="70"/>
@@ -7281,7 +7281,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="66"/>
       <c r="C53" s="22"/>
       <c r="D53" s="75"/>
@@ -7313,7 +7313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" ht="12.997499999999997" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="B54" s="66"/>
       <c r="C54" s="22"/>
       <c r="D54" s="67" t="s">
@@ -7347,7 +7347,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" ht="12.997499999999997" customHeight="1">
+    <row r="55" ht="12.75" customHeight="1">
       <c r="B55" s="66"/>
       <c r="C55" s="22"/>
       <c r="D55" s="49"/>
@@ -7379,7 +7379,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="56" ht="12.997499999999997" customHeight="1">
+    <row r="56" ht="12.75" customHeight="1">
       <c r="B56" s="66"/>
       <c r="C56" s="22"/>
       <c r="D56" s="49"/>
@@ -7411,7 +7411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57" ht="12.997499999999997" customHeight="1">
+    <row r="57" ht="12.75" customHeight="1">
       <c r="B57" s="66"/>
       <c r="C57" s="22"/>
       <c r="D57" s="49"/>
@@ -7475,15 +7475,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59" ht="12.997499999999997" customHeight="1">
+    <row r="59" ht="12.75" customHeight="1">
       <c r="L59" s="94"/>
     </row>
-    <row r="60" ht="12.997499999999997" customHeight="1">
+    <row r="60" ht="12.75" customHeight="1">
       <c r="E60" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="12.997499999999997" customHeight="1">
+    <row r="61" ht="12.75" customHeight="1">
       <c r="E61" s="7" t="s">
         <v>3</v>
       </c>
@@ -7526,7 +7526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F59F3BBE-0BAA-423E-A708-E7A1CA163421}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{1BB943DF-0B3F-492D-ADA5-4C70E8061E1C}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7556,7 +7556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="21"/>
       <c r="C4" s="6"/>
       <c r="D4" s="22"/>
@@ -7646,7 +7646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="21"/>
       <c r="C5" s="6"/>
       <c r="D5" s="22"/>
@@ -7678,7 +7678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="21"/>
       <c r="C6" s="6"/>
       <c r="D6" s="22"/>
@@ -7724,7 +7724,7 @@
       <c r="L7" s="31"/>
       <c r="M7" s="32"/>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="58" t="s">
         <v>90</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="101"/>
@@ -7790,7 +7790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
       <c r="D10" s="55" t="s">
@@ -7824,7 +7824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="49"/>
@@ -7856,7 +7856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="26"/>
@@ -7888,7 +7888,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
       <c r="D13" s="55" t="s">
@@ -7922,7 +7922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="102"/>
       <c r="C14" s="103"/>
       <c r="D14" s="26"/>
@@ -7968,7 +7968,7 @@
       <c r="L15" s="31"/>
       <c r="M15" s="32"/>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="58" t="s">
         <v>37</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="17" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A17" s="61"/>
       <c r="B17" s="21"/>
       <c r="C17" s="6"/>
@@ -8033,7 +8033,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="18" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A18" s="61"/>
       <c r="B18" s="102"/>
       <c r="C18" s="104"/>
@@ -8080,7 +8080,7 @@
       <c r="L19" s="31"/>
       <c r="M19" s="32"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="58" t="s">
         <v>42</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="21"/>
       <c r="C21" s="6"/>
       <c r="D21" s="22"/>
@@ -8146,7 +8146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="21"/>
       <c r="C22" s="6"/>
       <c r="D22" s="22"/>
@@ -8178,7 +8178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="21"/>
       <c r="C23" s="6"/>
       <c r="D23" s="22"/>
@@ -8210,7 +8210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="21"/>
       <c r="C24" s="6"/>
       <c r="D24" s="22"/>
@@ -8242,7 +8242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="102"/>
       <c r="C25" s="104"/>
       <c r="D25" s="103"/>
@@ -8288,7 +8288,7 @@
       <c r="L26" s="31"/>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="105" t="s">
         <v>93</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="66"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
@@ -8358,7 +8358,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="66"/>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -8390,7 +8390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="66"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -8422,7 +8422,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="66"/>
       <c r="C31" s="49"/>
       <c r="D31" s="49"/>
@@ -8454,7 +8454,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="66"/>
       <c r="C32" s="49"/>
       <c r="D32" s="49"/>
@@ -8486,7 +8486,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="66"/>
       <c r="C33" s="49"/>
       <c r="D33" s="26"/>
@@ -8518,7 +8518,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="66"/>
       <c r="C34" s="49"/>
       <c r="D34" s="67" t="s">
@@ -8552,7 +8552,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="66"/>
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
@@ -8584,7 +8584,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="66"/>
       <c r="C36" s="49"/>
       <c r="D36" s="49"/>
@@ -8616,7 +8616,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="66"/>
       <c r="C37" s="49"/>
       <c r="D37" s="49"/>
@@ -8748,7 +8748,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="66"/>
       <c r="C41" s="49"/>
       <c r="D41" s="70"/>
@@ -8780,7 +8780,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="66"/>
       <c r="C42" s="49"/>
       <c r="D42" s="70"/>
@@ -8812,7 +8812,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="66"/>
       <c r="C43" s="49"/>
       <c r="D43" s="70"/>
@@ -8844,7 +8844,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="66"/>
       <c r="C44" s="49"/>
       <c r="D44" s="70"/>
@@ -8876,7 +8876,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="66"/>
       <c r="C45" s="49"/>
       <c r="D45" s="70"/>
@@ -8908,7 +8908,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="66"/>
       <c r="C46" s="49"/>
       <c r="D46" s="75"/>
@@ -8940,7 +8940,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="66"/>
       <c r="C47" s="49"/>
       <c r="D47" s="67" t="s">
@@ -8974,7 +8974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="66"/>
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
@@ -9006,7 +9006,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="66"/>
       <c r="C49" s="49"/>
       <c r="D49" s="49"/>
@@ -9038,7 +9038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="66"/>
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
@@ -9102,15 +9102,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="L52" s="115"/>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="E53" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="12.997499999999997" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="E54" s="7" t="s">
         <v>3</v>
       </c>
@@ -9153,7 +9153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{12E7EFD1-8D40-453D-915A-386990105045}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F386B18A-9AD3-4EA1-B852-1AD0E3FC0EE8}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9183,7 +9183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="117" t="s">
         <v>99</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="21"/>
       <c r="C5" s="6"/>
       <c r="D5" s="22"/>
@@ -9307,7 +9307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="102"/>
       <c r="C6" s="104"/>
       <c r="D6" s="103"/>
@@ -9353,7 +9353,7 @@
       <c r="L7" s="31"/>
       <c r="M7" s="32"/>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="58" t="s">
         <v>90</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="101"/>
@@ -9419,7 +9419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
       <c r="D10" s="55" t="s">
@@ -9453,7 +9453,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="26"/>
@@ -9485,7 +9485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="55" t="s">
@@ -9519,7 +9519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="102"/>
       <c r="C13" s="103"/>
       <c r="D13" s="26"/>
@@ -9565,7 +9565,7 @@
       <c r="L14" s="31"/>
       <c r="M14" s="32"/>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="58" t="s">
         <v>37</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="21"/>
       <c r="C16" s="6"/>
       <c r="D16" s="22"/>
@@ -9631,7 +9631,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="17" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A17" s="61"/>
       <c r="B17" s="21"/>
       <c r="C17" s="6"/>
@@ -9664,7 +9664,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="18" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A18" s="61"/>
       <c r="B18" s="102"/>
       <c r="C18" s="104"/>
@@ -9711,7 +9711,7 @@
       <c r="L19" s="31"/>
       <c r="M19" s="32"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="58" t="s">
         <v>42</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="21"/>
       <c r="C21" s="6"/>
       <c r="D21" s="22"/>
@@ -9777,7 +9777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="21"/>
       <c r="C22" s="6"/>
       <c r="D22" s="22"/>
@@ -9809,7 +9809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="21"/>
       <c r="C23" s="6"/>
       <c r="D23" s="22"/>
@@ -9841,7 +9841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="21"/>
       <c r="C24" s="6"/>
       <c r="D24" s="22"/>
@@ -9873,7 +9873,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="102"/>
       <c r="C25" s="104"/>
       <c r="D25" s="103"/>
@@ -9919,7 +9919,7 @@
       <c r="L26" s="31"/>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="105" t="s">
         <v>93</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="66"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
@@ -9989,7 +9989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="66"/>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -10021,7 +10021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="66"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -10053,7 +10053,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="66"/>
       <c r="C31" s="49"/>
       <c r="D31" s="49"/>
@@ -10085,7 +10085,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="66"/>
       <c r="C32" s="49"/>
       <c r="D32" s="49"/>
@@ -10117,7 +10117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="66"/>
       <c r="C33" s="49"/>
       <c r="D33" s="26"/>
@@ -10149,7 +10149,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="66"/>
       <c r="C34" s="49"/>
       <c r="D34" s="67" t="s">
@@ -10183,7 +10183,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="66"/>
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
@@ -10215,7 +10215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="66"/>
       <c r="C36" s="49"/>
       <c r="D36" s="49"/>
@@ -10315,7 +10315,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="66"/>
       <c r="C39" s="49"/>
       <c r="D39" s="49"/>
@@ -10347,7 +10347,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="66"/>
       <c r="C40" s="49"/>
       <c r="D40" s="49"/>
@@ -10379,7 +10379,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="66"/>
       <c r="C41" s="49"/>
       <c r="D41" s="49"/>
@@ -10411,7 +10411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="66"/>
       <c r="C42" s="49"/>
       <c r="D42" s="49"/>
@@ -10443,7 +10443,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="66"/>
       <c r="C43" s="49"/>
       <c r="D43" s="49"/>
@@ -10475,7 +10475,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="66"/>
       <c r="C44" s="49"/>
       <c r="D44" s="49"/>
@@ -10507,7 +10507,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="66"/>
       <c r="C45" s="49"/>
       <c r="D45" s="49"/>
@@ -10539,7 +10539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="66"/>
       <c r="C46" s="49"/>
       <c r="D46" s="26"/>
@@ -10571,7 +10571,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="66"/>
       <c r="C47" s="49"/>
       <c r="D47" s="67" t="s">
@@ -10605,7 +10605,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="66"/>
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
@@ -10637,7 +10637,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="66"/>
       <c r="C49" s="49"/>
       <c r="D49" s="49"/>
@@ -10669,7 +10669,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="66"/>
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
@@ -10733,15 +10733,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="L52" s="115"/>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="E53" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="12.997499999999997" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="E54" s="7" t="s">
         <v>3</v>
       </c>
@@ -10785,7 +10785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{91F23718-9747-4567-994C-8FED5522B4D8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7CDE4B92-063D-470F-AEC9-B95F6DAC5474}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="12.997499999999997" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -10808,7 +10808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="119" t="s">
         <v>5</v>
       </c>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="L2" s="121"/>
     </row>
-    <row r="3" ht="12.997499999999997" customHeight="1">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="B3" s="119"/>
       <c r="C3" s="119"/>
       <c r="D3" s="119" t="s">
@@ -10866,7 +10866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="23" t="s">
         <v>89</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="12.997499999999997" customHeight="1">
+    <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="23" t="s">
         <v>108</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -11019,7 +11019,7 @@
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="23" t="s">
         <v>24</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="23" t="s">
         <v>96</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="23" t="s">
         <v>30</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="23" t="s">
         <v>32</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="23" t="s">
         <v>29</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -11207,7 +11207,7 @@
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="23" t="s">
         <v>38</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="23" t="s">
         <v>102</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="23" t="s">
         <v>39</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="18" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A18" s="61"/>
       <c r="B18" s="23" t="s">
         <v>91</v>
@@ -11348,7 +11348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="12.997499999999997" customHeight="1">
+    <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -11361,7 +11361,7 @@
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="23" t="s">
         <v>25</v>
       </c>
@@ -11396,7 +11396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="23" t="s">
         <v>23</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="23" t="s">
         <v>21</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="23" t="s">
         <v>56</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="23" t="s">
         <v>43</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="23" t="s">
         <v>44</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="12.997499999999997" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="B26" s="23" t="s">
         <v>92</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -11619,7 +11619,7 @@
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="23" t="s">
         <v>86</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="23" t="s">
         <v>46</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="23" t="s">
         <v>51</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="23" t="s">
         <v>52</v>
       </c>
@@ -11759,7 +11759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="23" t="s">
         <v>67</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="23" t="s">
         <v>53</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="23" t="s">
         <v>54</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -11877,7 +11877,7 @@
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="23" t="s">
         <v>45</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="23" t="s">
         <v>58</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" ht="12.997499999999997" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="B38" s="23" t="s">
         <v>59</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="23" t="s">
         <v>60</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -12030,7 +12030,7 @@
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="23" t="s">
         <v>77</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="23" t="s">
         <v>49</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="23" t="s">
         <v>75</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="23" t="s">
         <v>66</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="23" t="s">
         <v>40</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="23" t="s">
         <v>69</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="23" t="s">
         <v>103</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="39" t="s">
         <v>70</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="122"/>
@@ -12323,7 +12323,7 @@
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="23" t="s">
         <v>79</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" ht="12.997499999999997" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="39" t="s">
         <v>78</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="23" t="s">
         <v>68</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="23" t="s">
         <v>80</v>
       </c>
@@ -12484,7 +12484,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{38F4113E-CA38-4E41-8672-DDC0B526E5FA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DA7EEFBF-FCEC-4337-99DD-1F70A487AED7}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="12.997499999999997" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -12496,7 +12496,7 @@
     <col min="11" max="11" style="2" width="9.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.997499999999997" customHeight="1">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="C1" s="2" t="s">
         <v>118</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="119" t="s">
         <v>5</v>
       </c>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="J2" s="121"/>
     </row>
-    <row r="3" ht="12.997499999999997" customHeight="1">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="B3" s="119"/>
       <c r="C3" s="119"/>
       <c r="D3" s="119" t="s">
@@ -12555,7 +12555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="23" t="s">
         <v>89</v>
       </c>
@@ -12576,7 +12576,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
@@ -12597,7 +12597,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="23" t="s">
         <v>108</v>
       </c>
@@ -12614,7 +12614,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" ht="12.997499999999997" customHeight="1">
+    <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -12625,7 +12625,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="23" t="s">
         <v>18</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="23" t="s">
         <v>32</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="23" t="s">
         <v>24</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="23" t="s">
         <v>96</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="23" t="s">
         <v>120</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="23" t="s">
         <v>30</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="23" t="s">
         <v>29</v>
       </c>
@@ -12828,7 +12828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -12839,7 +12839,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="23" t="s">
         <v>38</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="23" t="s">
         <v>102</v>
       </c>
@@ -12897,7 +12897,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="18" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A18" s="61"/>
       <c r="B18" s="23" t="s">
         <v>121</v>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="K18" s="61"/>
     </row>
-    <row r="19" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="19" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A19" s="61"/>
       <c r="B19" s="23" t="s">
         <v>91</v>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="K19" s="61"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -12970,7 +12970,7 @@
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="23" t="s">
         <v>25</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="23" t="s">
         <v>23</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="23" t="s">
         <v>21</v>
       </c>
@@ -13057,7 +13057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="23" t="s">
         <v>56</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="23" t="s">
         <v>43</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" ht="12.997499999999997" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="B26" s="23" t="s">
         <v>44</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="23" t="s">
         <v>92</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -13184,7 +13184,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="23" t="s">
         <v>86</v>
       </c>
@@ -13213,7 +13213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="23" t="s">
         <v>46</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="23" t="s">
         <v>49</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="23" t="s">
         <v>51</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="23" t="s">
         <v>52</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="23" t="s">
         <v>53</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="23" t="s">
         <v>54</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
@@ -13398,7 +13398,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="23" t="s">
         <v>45</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" ht="12.997499999999997" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="B38" s="23" t="s">
         <v>58</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="23" t="s">
         <v>59</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="23" t="s">
         <v>60</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -13525,7 +13525,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="23" t="s">
         <v>75</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="23" t="s">
         <v>77</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="23" t="s">
         <v>67</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="23" t="s">
         <v>66</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="23" t="s">
         <v>40</v>
       </c>
@@ -13670,7 +13670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="23" t="s">
         <v>69</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="23" t="s">
         <v>103</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="122"/>
@@ -13739,7 +13739,7 @@
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="23" t="s">
         <v>39</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" ht="12.997499999999997" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="23" t="s">
         <v>79</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="23" t="s">
         <v>68</v>
       </c>
@@ -13826,7 +13826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="23" t="s">
         <v>80</v>
       </c>
@@ -13875,7 +13875,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{98EE065D-21AF-4137-A092-FFF7479D8AEC}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EBB0C33F-E422-4946-B28E-9641C44C276A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="12.997499999999997" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -13886,7 +13886,7 @@
     <col min="9" max="10" style="2" width="12.421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.997499999999997" customHeight="1">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="C1" s="2" t="s">
         <v>118</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="B2" s="119" t="s">
         <v>5</v>
       </c>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="J2" s="121"/>
     </row>
-    <row r="3" ht="12.997499999999997" customHeight="1">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="B3" s="119"/>
       <c r="C3" s="119"/>
       <c r="D3" s="119" t="s">
@@ -13945,7 +13945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="23" t="s">
         <v>89</v>
       </c>
@@ -13966,7 +13966,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
@@ -13987,7 +13987,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="23" t="s">
         <v>108</v>
       </c>
@@ -14004,7 +14004,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" ht="12.997499999999997" customHeight="1">
+    <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -14015,7 +14015,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="23" t="s">
         <v>18</v>
       </c>
@@ -14044,7 +14044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="23" t="s">
         <v>32</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="23" t="s">
         <v>24</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="23" t="s">
         <v>96</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="23" t="s">
         <v>120</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="23" t="s">
         <v>30</v>
       </c>
@@ -14189,7 +14189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="23" t="s">
         <v>29</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -14229,7 +14229,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="23" t="s">
         <v>91</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="23" t="s">
         <v>38</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1">
+    <row r="18" ht="12.75" customHeight="1">
       <c r="B18" s="23" t="s">
         <v>102</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="19" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A19" s="61"/>
       <c r="B19" s="23" t="s">
         <v>121</v>
@@ -14346,7 +14346,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -14357,7 +14357,7 @@
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="23" t="s">
         <v>25</v>
       </c>
@@ -14386,7 +14386,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="23" t="s">
         <v>23</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="23" t="s">
         <v>21</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="23" t="s">
         <v>56</v>
       </c>
@@ -14473,7 +14473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="23" t="s">
         <v>43</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" ht="12.997499999999997" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="B26" s="23" t="s">
         <v>44</v>
       </c>
@@ -14531,7 +14531,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="23" t="s">
         <v>92</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -14571,7 +14571,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="23" t="s">
         <v>86</v>
       </c>
@@ -14600,7 +14600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="23" t="s">
         <v>46</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="23" t="s">
         <v>49</v>
       </c>
@@ -14658,7 +14658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="23" t="s">
         <v>51</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="23" t="s">
         <v>52</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="23" t="s">
         <v>53</v>
       </c>
@@ -14745,7 +14745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="23" t="s">
         <v>54</v>
       </c>
@@ -14774,7 +14774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
@@ -14785,7 +14785,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="23" t="s">
         <v>45</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" ht="12.997499999999997" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="B38" s="23" t="s">
         <v>58</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="23" t="s">
         <v>59</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="23" t="s">
         <v>60</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -14912,7 +14912,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="23" t="s">
         <v>75</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="23" t="s">
         <v>77</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="23" t="s">
         <v>67</v>
       </c>
@@ -14999,7 +14999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="23" t="s">
         <v>66</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="23" t="s">
         <v>40</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="23" t="s">
         <v>69</v>
       </c>
@@ -15086,7 +15086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="23" t="s">
         <v>103</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="122"/>
@@ -15126,7 +15126,7 @@
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="23" t="s">
         <v>39</v>
       </c>
@@ -15155,7 +15155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" ht="12.997499999999997" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="23" t="s">
         <v>79</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="23" t="s">
         <v>68</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="23" t="s">
         <v>80</v>
       </c>
@@ -15262,7 +15262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B06CB4E5-089D-46A7-9449-DA80D56D8AF4}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{90038EAC-5F79-4045-B88D-F1A2F69A13F6}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="12.997499999999997" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -15273,7 +15273,7 @@
     <col min="11" max="11" style="2" width="9.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.997499999999997" customHeight="1">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="B1" s="2" t="s">
         <v>123</v>
       </c>
@@ -15284,7 +15284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.997499999999997" customHeight="1">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="119" t="s">
         <v>5</v>
       </c>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="J2" s="121"/>
     </row>
-    <row r="3" ht="12.997499999999997" customHeight="1">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="119"/>
       <c r="B3" s="119"/>
       <c r="C3" s="119" t="s">
@@ -15336,7 +15336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="12.997499999999997" customHeight="1">
+    <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="23" t="s">
         <v>89</v>
       </c>
@@ -15360,7 +15360,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" ht="12.997499999999997" customHeight="1">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>108</v>
       </c>
@@ -15384,7 +15384,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" ht="12.997499999999997" customHeight="1">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
@@ -15396,7 +15396,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" ht="12.997499999999997" customHeight="1">
+    <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="23" t="s">
         <v>19</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" ht="12.997499999999997" customHeight="1">
+    <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23" t="s">
         <v>102</v>
       </c>
@@ -15460,7 +15460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="12.997499999999997" customHeight="1">
+    <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="23" t="s">
         <v>96</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" ht="12.997499999999997" customHeight="1">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -15504,7 +15504,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
-    <row r="11" ht="12.997499999999997" customHeight="1">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23" t="s">
         <v>18</v>
       </c>
@@ -15536,7 +15536,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" ht="12.997499999999997" customHeight="1">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="23" t="s">
         <v>32</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="12.997499999999997" customHeight="1">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="23" t="s">
         <v>24</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="12.997499999999997" customHeight="1">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="23" t="s">
         <v>120</v>
       </c>
@@ -15632,7 +15632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="12.997499999999997" customHeight="1">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="23" t="s">
         <v>30</v>
       </c>
@@ -15664,7 +15664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="12.997499999999997" customHeight="1">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="23" t="s">
         <v>29</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" ht="12.997499999999997" customHeight="1">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -15708,7 +15708,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" ht="12.997499999999997" customHeight="1">
+    <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="23" t="s">
         <v>91</v>
       </c>
@@ -15740,7 +15740,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" ht="12.997499999999997" customHeight="1">
+    <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="23" t="s">
         <v>129</v>
       </c>
@@ -15765,7 +15765,7 @@
       <c r="J19" s="23"/>
       <c r="K19" s="124"/>
     </row>
-    <row r="20" ht="12.997499999999997" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="23" t="s">
         <v>38</v>
       </c>
@@ -15797,7 +15797,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" ht="12.997499999999997" customHeight="1" s="61" customFormat="1">
+    <row r="21" ht="12.75" customHeight="1" s="61" customFormat="1">
       <c r="A21" s="23" t="s">
         <v>121</v>
       </c>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K21" s="61"/>
     </row>
-    <row r="22" ht="12.997499999999997" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="125"/>
       <c r="B22" s="125"/>
       <c r="C22" s="125"/>
@@ -15842,7 +15842,7 @@
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
     </row>
-    <row r="23" ht="12.997499999999997" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="125" t="s">
         <v>25</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" ht="12.997499999999997" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="125" t="s">
         <v>23</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" ht="12.997499999999997" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="125" t="s">
         <v>21</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" ht="12.997499999999997" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="125" t="s">
         <v>56</v>
       </c>
@@ -15970,7 +15970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" ht="12.997499999999997" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="39" t="s">
         <v>92</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="12.997499999999997" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="125"/>
       <c r="B28" s="125"/>
       <c r="C28" s="125"/>
@@ -16014,7 +16014,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" ht="12.997499999999997" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="23" t="s">
         <v>86</v>
       </c>
@@ -16046,7 +16046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="12.997499999999997" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="23" t="s">
         <v>46</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" ht="12.997499999999997" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="23" t="s">
         <v>49</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" ht="12.997499999999997" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="23" t="s">
         <v>51</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" ht="12.997499999999997" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23" t="s">
         <v>52</v>
       </c>
@@ -16174,7 +16174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" ht="12.997499999999997" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23" t="s">
         <v>53</v>
       </c>
@@ -16206,7 +16206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" ht="12.997499999999997" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="39" t="s">
         <v>54</v>
       </c>
@@ -16238,7 +16238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" ht="12.997499999999997" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="125"/>
       <c r="B36" s="125"/>
       <c r="C36" s="125"/>
@@ -16250,7 +16250,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" ht="12.997499999999997" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23" t="s">
         <v>43</v>
       </c>
@@ -16282,7 +16282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" ht="12.997499999999997" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23" t="s">
         <v>45</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" ht="12.997499999999997" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23" t="s">
         <v>58</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" ht="12.997499999999997" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="23" t="s">
         <v>59</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" ht="12.997499999999997" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="125"/>
       <c r="B41" s="125"/>
       <c r="C41" s="125"/>
@@ -16390,7 +16390,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" ht="12.997499999999997" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="125" t="s">
         <v>44</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="12.997499999999997" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="125" t="s">
         <v>75</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="12.997499999999997" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="125" t="s">
         <v>77</v>
       </c>
@@ -16486,7 +16486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="12.997499999999997" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="125" t="s">
         <v>133</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="12.997499999999997" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="125" t="s">
         <v>67</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="12.997499999999997" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="125" t="s">
         <v>66</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="12.997499999999997" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="125" t="s">
         <v>69</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" ht="12.997499999999997" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="23" t="s">
         <v>40</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" ht="12.997499999999997" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="125"/>
       <c r="B50" s="125"/>
       <c r="C50" s="126"/>
@@ -16658,7 +16658,7 @@
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
     </row>
-    <row r="51" ht="12.997499999999997" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="125" t="s">
         <v>39</v>
       </c>
@@ -16690,7 +16690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="12.997499999999997" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="125" t="s">
         <v>79</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="12.997499999999997" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="125" t="s">
         <v>68</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" ht="12.997499999999997" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="23" t="s">
         <v>80</v>
       </c>
